--- a/cp-card-custodian/ig/all-profiles.xlsx
+++ b/cp-card-custodian/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1337">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T15:58:57+00:00</t>
+    <t>2026-05-05T16:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -825,7 +825,7 @@
 </t>
   </si>
   <si>
-    <t>Organization which maintains the document</t>
+    <t>Organisme responsable de la gestion du document. Information transmise dans le VIHF.</t>
   </si>
   <si>
     <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
@@ -3898,6 +3898,9 @@
   </si>
   <si>
     <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif.</t>
+  </si>
+  <si>
+    <t>Organization which maintains the document</t>
   </si>
   <si>
     <t>Relationships to other documents</t>
@@ -5666,7 +5669,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="174">
@@ -5674,7 +5677,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="175">
@@ -5690,7 +5693,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="177">
@@ -5698,7 +5701,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="178">
@@ -5752,7 +5755,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="185">
@@ -5796,7 +5799,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="191">
@@ -9016,7 +9019,7 @@
       </c>
       <c r="F31" s="2"/>
       <c r="G31" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -73865,7 +73868,7 @@
         <v>254</v>
       </c>
       <c r="M652" t="s" s="2">
-        <v>255</v>
+        <v>1245</v>
       </c>
       <c r="N652" t="s" s="2">
         <v>256</v>
@@ -73970,10 +73973,10 @@
         <v>259</v>
       </c>
       <c r="M653" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="N653" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>262</v>
@@ -74390,7 +74393,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>274</v>
@@ -74495,7 +74498,7 @@
         <v>279</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>281</v>
@@ -74812,7 +74815,7 @@
         <v>259</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>296</v>
@@ -75751,7 +75754,7 @@
         <v>321</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>323</v>
@@ -75858,7 +75861,7 @@
         <v>328</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>330</v>
@@ -76284,7 +76287,7 @@
         <v>356</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>358</v>
@@ -77287,7 +77290,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="685">
@@ -77392,7 +77395,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="686">
@@ -77605,7 +77608,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1099</v>
@@ -77708,7 +77711,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1101</v>
@@ -77813,7 +77816,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1102</v>
@@ -77916,7 +77919,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1103</v>
@@ -78019,7 +78022,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1104</v>
@@ -78124,7 +78127,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1105</v>
@@ -78229,7 +78232,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1106</v>
@@ -78334,7 +78337,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1107</v>
@@ -78439,7 +78442,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1108</v>
@@ -78544,7 +78547,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1109</v>
@@ -78649,7 +78652,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1110</v>
@@ -78754,7 +78757,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1111</v>
@@ -78859,7 +78862,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1112</v>
@@ -78964,7 +78967,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1113</v>
@@ -79069,7 +79072,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1114</v>
@@ -79101,7 +79104,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79174,7 +79177,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1116</v>
@@ -79188,7 +79191,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79275,7 +79278,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1117</v>
@@ -79309,7 +79312,7 @@
         <v>1119</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1121</v>
@@ -79375,18 +79378,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C705" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79483,13 +79486,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C706" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79586,13 +79589,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C707" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79632,7 +79635,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79691,13 +79694,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C708" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79757,13 +79760,13 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="AB708" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AC708" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="AD708" s="2"/>
       <c r="AE708" t="s" s="2">
@@ -79790,16 +79793,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C709" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79895,16 +79898,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79926,13 +79929,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="M710" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N710" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -80000,16 +80003,16 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D711" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="E711" t="s" s="2">
         <v>75</v>
@@ -80031,13 +80034,13 @@
         <v>75</v>
       </c>
       <c r="L711" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N711" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="O711" s="2"/>
       <c r="P711" s="2"/>
@@ -80105,10 +80108,10 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1116</v>
@@ -80139,7 +80142,7 @@
         <v>187</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>189</v>
@@ -80210,16 +80213,16 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C713" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D713" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="E713" t="s" s="2">
         <v>75</v>
@@ -80241,10 +80244,10 @@
         <v>75</v>
       </c>
       <c r="L713" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="M713" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N713" t="s" s="2">
         <v>994</v>
@@ -80315,13 +80318,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80418,13 +80421,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80521,13 +80524,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80626,13 +80629,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -80655,7 +80658,7 @@
         <v>75</v>
       </c>
       <c r="L717" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="M717" t="s" s="2">
         <v>1007</v>
@@ -80729,7 +80732,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1122</v>
@@ -80832,7 +80835,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1123</v>
@@ -80933,7 +80936,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1126</v>
@@ -80964,10 +80967,10 @@
         <v>75</v>
       </c>
       <c r="L720" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>196</v>
@@ -81038,7 +81041,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1129</v>
@@ -81072,7 +81075,7 @@
         <v>206</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>196</v>
@@ -81143,7 +81146,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1131</v>
@@ -81175,7 +81178,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1133</v>
@@ -81248,7 +81251,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1137</v>
@@ -81280,7 +81283,7 @@
         <v>159</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1139</v>
@@ -81355,7 +81358,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1145</v>
@@ -81387,7 +81390,7 @@
         <v>98</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1147</v>
@@ -81460,7 +81463,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1150</v>
@@ -81492,7 +81495,7 @@
         <v>221</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1152</v>
@@ -81511,7 +81514,7 @@
         <v>75</v>
       </c>
       <c r="T725" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="U725" t="s" s="2">
         <v>75</v>
@@ -81565,7 +81568,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1157</v>
@@ -81672,7 +81675,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81775,7 +81778,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1166</v>
@@ -81807,7 +81810,7 @@
         <v>356</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1168</v>
@@ -81882,7 +81885,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1171</v>
@@ -81914,7 +81917,7 @@
         <v>244</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="N729" t="s" s="2">
         <v>1175</v>
@@ -81989,13 +81992,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82092,13 +82095,13 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D731" s="2"/>
       <c r="E731" t="s" s="2">
@@ -82197,16 +82200,16 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1311</v>
+      </c>
+      <c r="C732" t="s" s="2">
         <v>1310</v>
       </c>
-      <c r="C732" t="s" s="2">
-        <v>1309</v>
-      </c>
       <c r="D732" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="E732" t="s" s="2">
         <v>75</v>
@@ -82228,13 +82231,13 @@
         <v>75</v>
       </c>
       <c r="L732" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="M732" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="N732" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="O732" s="2"/>
       <c r="P732" s="2"/>
@@ -82302,13 +82305,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82405,13 +82408,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82508,13 +82511,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82554,7 +82557,7 @@
       </c>
       <c r="R735" s="2"/>
       <c r="S735" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="T735" t="s" s="2">
         <v>75</v>
@@ -82613,13 +82616,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82642,7 +82645,7 @@
         <v>75</v>
       </c>
       <c r="L736" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="M736" t="s" s="2">
         <v>1007</v>
@@ -82687,7 +82690,7 @@
         <v>75</v>
       </c>
       <c r="AC736" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="AD736" s="2"/>
       <c r="AE736" t="s" s="2">
@@ -82714,16 +82717,16 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D737" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E737" t="s" s="2">
         <v>75</v>
@@ -82745,7 +82748,7 @@
         <v>75</v>
       </c>
       <c r="L737" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="M737" t="s" s="2">
         <v>1007</v>
@@ -82819,13 +82822,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82924,13 +82927,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83029,13 +83032,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83134,13 +83137,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83239,7 +83242,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1178</v>
@@ -83346,7 +83349,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1185</v>
@@ -83378,7 +83381,7 @@
         <v>1186</v>
       </c>
       <c r="M743" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="N743" t="s" s="2">
         <v>1188</v>
@@ -83449,7 +83452,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1189</v>
@@ -83481,7 +83484,7 @@
         <v>259</v>
       </c>
       <c r="M744" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="N744" t="s" s="2">
         <v>1191</v>
@@ -83554,7 +83557,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1194</v>
@@ -83657,7 +83660,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1195</v>
@@ -83762,7 +83765,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1196</v>
@@ -83869,7 +83872,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1197</v>
@@ -83976,7 +83979,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1204</v>
@@ -84085,7 +84088,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1211</v>
@@ -84190,7 +84193,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1215</v>
@@ -84219,10 +84222,10 @@
         <v>75</v>
       </c>
       <c r="L751" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="M751" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="N751" t="s" s="2">
         <v>1218</v>
@@ -84293,7 +84296,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1219</v>

--- a/cp-card-custodian/ig/all-profiles.xlsx
+++ b/cp-card-custodian/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1336">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T16:17:29+00:00</t>
+    <t>2026-05-06T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3898,9 +3898,6 @@
   </si>
   <si>
     <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif.</t>
-  </si>
-  <si>
-    <t>Organization which maintains the document</t>
   </si>
   <si>
     <t>Relationships to other documents</t>
@@ -5669,7 +5666,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="174">
@@ -5677,7 +5674,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="175">
@@ -5693,7 +5690,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="177">
@@ -5701,7 +5698,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="178">
@@ -5755,7 +5752,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="185">
@@ -5799,7 +5796,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="191">
@@ -73850,7 +73847,7 @@
       </c>
       <c r="F652" s="2"/>
       <c r="G652" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H652" t="s" s="2">
         <v>84</v>
@@ -73868,7 +73865,7 @@
         <v>254</v>
       </c>
       <c r="M652" t="s" s="2">
-        <v>1245</v>
+        <v>255</v>
       </c>
       <c r="N652" t="s" s="2">
         <v>256</v>
@@ -73973,10 +73970,10 @@
         <v>259</v>
       </c>
       <c r="M653" t="s" s="2">
+        <v>1245</v>
+      </c>
+      <c r="N653" t="s" s="2">
         <v>1246</v>
-      </c>
-      <c r="N653" t="s" s="2">
-        <v>1247</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>262</v>
@@ -74393,7 +74390,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>274</v>
@@ -74498,7 +74495,7 @@
         <v>279</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>281</v>
@@ -74815,7 +74812,7 @@
         <v>259</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>296</v>
@@ -75754,7 +75751,7 @@
         <v>321</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>323</v>
@@ -75861,7 +75858,7 @@
         <v>328</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>330</v>
@@ -76287,7 +76284,7 @@
         <v>356</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>358</v>
@@ -77290,7 +77287,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="685">
@@ -77395,7 +77392,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="686">
@@ -77608,7 +77605,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1099</v>
@@ -77711,7 +77708,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1101</v>
@@ -77816,7 +77813,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1102</v>
@@ -77919,7 +77916,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1103</v>
@@ -78022,7 +78019,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1104</v>
@@ -78127,7 +78124,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1105</v>
@@ -78232,7 +78229,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1106</v>
@@ -78337,7 +78334,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1107</v>
@@ -78442,7 +78439,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1108</v>
@@ -78547,7 +78544,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1109</v>
@@ -78652,7 +78649,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1110</v>
@@ -78757,7 +78754,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1111</v>
@@ -78862,7 +78859,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1112</v>
@@ -78967,7 +78964,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1113</v>
@@ -79072,7 +79069,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1114</v>
@@ -79104,7 +79101,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79177,7 +79174,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1116</v>
@@ -79191,7 +79188,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79278,7 +79275,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1117</v>
@@ -79312,7 +79309,7 @@
         <v>1119</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1121</v>
@@ -79378,18 +79375,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1264</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1265</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1266</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79486,13 +79483,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1266</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1267</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1268</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79589,13 +79586,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1268</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1269</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1270</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79635,7 +79632,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79694,13 +79691,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1271</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1272</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1273</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79760,13 +79757,13 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
+        <v>1273</v>
+      </c>
+      <c r="AB708" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC708" t="s" s="2">
         <v>1274</v>
-      </c>
-      <c r="AB708" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC708" t="s" s="2">
-        <v>1275</v>
       </c>
       <c r="AD708" s="2"/>
       <c r="AE708" t="s" s="2">
@@ -79793,16 +79790,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1275</v>
+      </c>
+      <c r="C709" t="s" s="2">
+        <v>1272</v>
+      </c>
+      <c r="D709" t="s" s="2">
         <v>1276</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1273</v>
-      </c>
-      <c r="D709" t="s" s="2">
-        <v>1277</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79898,16 +79895,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79929,13 +79926,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
+        <v>1279</v>
+      </c>
+      <c r="M710" t="s" s="2">
         <v>1280</v>
       </c>
-      <c r="M710" t="s" s="2">
+      <c r="N710" t="s" s="2">
         <v>1281</v>
-      </c>
-      <c r="N710" t="s" s="2">
-        <v>1282</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -80003,16 +80000,16 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D711" t="s" s="2">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E711" t="s" s="2">
         <v>75</v>
@@ -80034,13 +80031,13 @@
         <v>75</v>
       </c>
       <c r="L711" t="s" s="2">
+        <v>1284</v>
+      </c>
+      <c r="M711" t="s" s="2">
         <v>1285</v>
       </c>
-      <c r="M711" t="s" s="2">
+      <c r="N711" t="s" s="2">
         <v>1286</v>
-      </c>
-      <c r="N711" t="s" s="2">
-        <v>1287</v>
       </c>
       <c r="O711" s="2"/>
       <c r="P711" s="2"/>
@@ -80108,10 +80105,10 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1116</v>
@@ -80142,7 +80139,7 @@
         <v>187</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>189</v>
@@ -80213,16 +80210,16 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C713" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D713" t="s" s="2">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E713" t="s" s="2">
         <v>75</v>
@@ -80244,10 +80241,10 @@
         <v>75</v>
       </c>
       <c r="L713" t="s" s="2">
+        <v>1291</v>
+      </c>
+      <c r="M713" t="s" s="2">
         <v>1292</v>
-      </c>
-      <c r="M713" t="s" s="2">
-        <v>1293</v>
       </c>
       <c r="N713" t="s" s="2">
         <v>994</v>
@@ -80318,13 +80315,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80421,13 +80418,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80524,13 +80521,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80629,13 +80626,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -80658,7 +80655,7 @@
         <v>75</v>
       </c>
       <c r="L717" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="M717" t="s" s="2">
         <v>1007</v>
@@ -80732,7 +80729,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1122</v>
@@ -80835,7 +80832,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1123</v>
@@ -80936,7 +80933,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1126</v>
@@ -80967,10 +80964,10 @@
         <v>75</v>
       </c>
       <c r="L720" t="s" s="2">
+        <v>1298</v>
+      </c>
+      <c r="M720" t="s" s="2">
         <v>1299</v>
-      </c>
-      <c r="M720" t="s" s="2">
-        <v>1300</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>196</v>
@@ -81041,7 +81038,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1129</v>
@@ -81075,7 +81072,7 @@
         <v>206</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>196</v>
@@ -81146,7 +81143,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1131</v>
@@ -81178,7 +81175,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1133</v>
@@ -81251,7 +81248,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1137</v>
@@ -81283,7 +81280,7 @@
         <v>159</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1139</v>
@@ -81358,7 +81355,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1145</v>
@@ -81390,7 +81387,7 @@
         <v>98</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1147</v>
@@ -81463,7 +81460,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1150</v>
@@ -81495,7 +81492,7 @@
         <v>221</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1152</v>
@@ -81514,7 +81511,7 @@
         <v>75</v>
       </c>
       <c r="T725" t="s" s="2">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="U725" t="s" s="2">
         <v>75</v>
@@ -81568,7 +81565,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1157</v>
@@ -81675,7 +81672,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81778,7 +81775,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1166</v>
@@ -81810,7 +81807,7 @@
         <v>356</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1168</v>
@@ -81885,7 +81882,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1171</v>
@@ -81917,7 +81914,7 @@
         <v>244</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="N729" t="s" s="2">
         <v>1175</v>
@@ -81992,13 +81989,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82095,13 +82092,13 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="D731" s="2"/>
       <c r="E731" t="s" s="2">
@@ -82200,16 +82197,16 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1310</v>
+      </c>
+      <c r="C732" t="s" s="2">
+        <v>1309</v>
+      </c>
+      <c r="D732" t="s" s="2">
         <v>1311</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1310</v>
-      </c>
-      <c r="D732" t="s" s="2">
-        <v>1312</v>
       </c>
       <c r="E732" t="s" s="2">
         <v>75</v>
@@ -82231,13 +82228,13 @@
         <v>75</v>
       </c>
       <c r="L732" t="s" s="2">
+        <v>1312</v>
+      </c>
+      <c r="M732" t="s" s="2">
         <v>1313</v>
       </c>
-      <c r="M732" t="s" s="2">
+      <c r="N732" t="s" s="2">
         <v>1314</v>
-      </c>
-      <c r="N732" t="s" s="2">
-        <v>1315</v>
       </c>
       <c r="O732" s="2"/>
       <c r="P732" s="2"/>
@@ -82305,13 +82302,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1316</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1317</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82408,13 +82405,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1318</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1319</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82511,13 +82508,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1319</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1320</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1321</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82557,7 +82554,7 @@
       </c>
       <c r="R735" s="2"/>
       <c r="S735" t="s" s="2">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="T735" t="s" s="2">
         <v>75</v>
@@ -82616,13 +82613,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1322</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1323</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1324</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82645,7 +82642,7 @@
         <v>75</v>
       </c>
       <c r="L736" t="s" s="2">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="M736" t="s" s="2">
         <v>1007</v>
@@ -82690,7 +82687,7 @@
         <v>75</v>
       </c>
       <c r="AC736" t="s" s="2">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="AD736" s="2"/>
       <c r="AE736" t="s" s="2">
@@ -82717,16 +82714,16 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1325</v>
+      </c>
+      <c r="C737" t="s" s="2">
+        <v>1323</v>
+      </c>
+      <c r="D737" t="s" s="2">
         <v>1326</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1324</v>
-      </c>
-      <c r="D737" t="s" s="2">
-        <v>1327</v>
       </c>
       <c r="E737" t="s" s="2">
         <v>75</v>
@@ -82748,7 +82745,7 @@
         <v>75</v>
       </c>
       <c r="L737" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="M737" t="s" s="2">
         <v>1007</v>
@@ -82822,13 +82819,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82927,13 +82924,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83032,13 +83029,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83137,13 +83134,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83242,7 +83239,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1178</v>
@@ -83349,7 +83346,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1185</v>
@@ -83381,7 +83378,7 @@
         <v>1186</v>
       </c>
       <c r="M743" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="N743" t="s" s="2">
         <v>1188</v>
@@ -83452,7 +83449,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1189</v>
@@ -83484,7 +83481,7 @@
         <v>259</v>
       </c>
       <c r="M744" t="s" s="2">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="N744" t="s" s="2">
         <v>1191</v>
@@ -83557,7 +83554,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1194</v>
@@ -83660,7 +83657,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1195</v>
@@ -83765,7 +83762,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1196</v>
@@ -83872,7 +83869,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1197</v>
@@ -83979,7 +83976,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1204</v>
@@ -84088,7 +84085,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1211</v>
@@ -84193,7 +84190,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1215</v>
@@ -84222,10 +84219,10 @@
         <v>75</v>
       </c>
       <c r="L751" t="s" s="2">
+        <v>1334</v>
+      </c>
+      <c r="M751" t="s" s="2">
         <v>1335</v>
-      </c>
-      <c r="M751" t="s" s="2">
-        <v>1336</v>
       </c>
       <c r="N751" t="s" s="2">
         <v>1218</v>
@@ -84296,7 +84293,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1219</v>

--- a/cp-card-custodian/ig/all-profiles.xlsx
+++ b/cp-card-custodian/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1337">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T12:21:18+00:00</t>
+    <t>2026-05-27T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3898,6 +3898,9 @@
   </si>
   <si>
     <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif.</t>
+  </si>
+  <si>
+    <t>Organisme responsable de la gestion du document. Dans le cadre XDS, il s'agit d'une information transmise dans le VIHF.</t>
   </si>
   <si>
     <t>Relationships to other documents</t>
@@ -5666,7 +5669,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="174">
@@ -5674,7 +5677,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="175">
@@ -5690,7 +5693,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="177">
@@ -5698,7 +5701,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="178">
@@ -5752,7 +5755,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="185">
@@ -5796,7 +5799,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="191">
@@ -73865,7 +73868,7 @@
         <v>254</v>
       </c>
       <c r="M652" t="s" s="2">
-        <v>255</v>
+        <v>1245</v>
       </c>
       <c r="N652" t="s" s="2">
         <v>256</v>
@@ -73970,10 +73973,10 @@
         <v>259</v>
       </c>
       <c r="M653" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="N653" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>262</v>
@@ -74390,7 +74393,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>274</v>
@@ -74495,7 +74498,7 @@
         <v>279</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>281</v>
@@ -74812,7 +74815,7 @@
         <v>259</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>296</v>
@@ -75751,7 +75754,7 @@
         <v>321</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>323</v>
@@ -75858,7 +75861,7 @@
         <v>328</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>330</v>
@@ -76284,7 +76287,7 @@
         <v>356</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>358</v>
@@ -77287,7 +77290,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="685">
@@ -77392,7 +77395,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="686">
@@ -77605,7 +77608,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1099</v>
@@ -77708,7 +77711,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1101</v>
@@ -77813,7 +77816,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1102</v>
@@ -77916,7 +77919,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1103</v>
@@ -78019,7 +78022,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1104</v>
@@ -78124,7 +78127,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1105</v>
@@ -78229,7 +78232,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1106</v>
@@ -78334,7 +78337,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1107</v>
@@ -78439,7 +78442,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1108</v>
@@ -78544,7 +78547,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1109</v>
@@ -78649,7 +78652,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1110</v>
@@ -78754,7 +78757,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1111</v>
@@ -78859,7 +78862,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1112</v>
@@ -78964,7 +78967,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1113</v>
@@ -79069,7 +79072,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1114</v>
@@ -79101,7 +79104,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79174,7 +79177,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1116</v>
@@ -79188,7 +79191,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79275,7 +79278,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1117</v>
@@ -79309,7 +79312,7 @@
         <v>1119</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1121</v>
@@ -79375,18 +79378,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C705" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79483,13 +79486,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C706" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79586,13 +79589,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C707" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79632,7 +79635,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79691,13 +79694,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C708" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79757,13 +79760,13 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="AB708" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AC708" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="AD708" s="2"/>
       <c r="AE708" t="s" s="2">
@@ -79790,16 +79793,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C709" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79895,16 +79898,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79926,13 +79929,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="M710" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N710" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -80000,16 +80003,16 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D711" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="E711" t="s" s="2">
         <v>75</v>
@@ -80031,13 +80034,13 @@
         <v>75</v>
       </c>
       <c r="L711" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N711" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="O711" s="2"/>
       <c r="P711" s="2"/>
@@ -80105,10 +80108,10 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1116</v>
@@ -80139,7 +80142,7 @@
         <v>187</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>189</v>
@@ -80210,16 +80213,16 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C713" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D713" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="E713" t="s" s="2">
         <v>75</v>
@@ -80241,10 +80244,10 @@
         <v>75</v>
       </c>
       <c r="L713" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="M713" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N713" t="s" s="2">
         <v>994</v>
@@ -80315,13 +80318,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80418,13 +80421,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80521,13 +80524,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80626,13 +80629,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -80655,7 +80658,7 @@
         <v>75</v>
       </c>
       <c r="L717" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="M717" t="s" s="2">
         <v>1007</v>
@@ -80729,7 +80732,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1122</v>
@@ -80832,7 +80835,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1123</v>
@@ -80933,7 +80936,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1126</v>
@@ -80964,10 +80967,10 @@
         <v>75</v>
       </c>
       <c r="L720" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>196</v>
@@ -81038,7 +81041,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1129</v>
@@ -81072,7 +81075,7 @@
         <v>206</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>196</v>
@@ -81143,7 +81146,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1131</v>
@@ -81175,7 +81178,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1133</v>
@@ -81248,7 +81251,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1137</v>
@@ -81280,7 +81283,7 @@
         <v>159</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1139</v>
@@ -81355,7 +81358,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1145</v>
@@ -81387,7 +81390,7 @@
         <v>98</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1147</v>
@@ -81460,7 +81463,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1150</v>
@@ -81492,7 +81495,7 @@
         <v>221</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1152</v>
@@ -81511,7 +81514,7 @@
         <v>75</v>
       </c>
       <c r="T725" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="U725" t="s" s="2">
         <v>75</v>
@@ -81565,7 +81568,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1157</v>
@@ -81672,7 +81675,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81775,7 +81778,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1166</v>
@@ -81807,7 +81810,7 @@
         <v>356</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1168</v>
@@ -81882,7 +81885,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1171</v>
@@ -81914,7 +81917,7 @@
         <v>244</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="N729" t="s" s="2">
         <v>1175</v>
@@ -81989,13 +81992,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82092,13 +82095,13 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D731" s="2"/>
       <c r="E731" t="s" s="2">
@@ -82197,16 +82200,16 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1311</v>
+      </c>
+      <c r="C732" t="s" s="2">
         <v>1310</v>
       </c>
-      <c r="C732" t="s" s="2">
-        <v>1309</v>
-      </c>
       <c r="D732" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="E732" t="s" s="2">
         <v>75</v>
@@ -82228,13 +82231,13 @@
         <v>75</v>
       </c>
       <c r="L732" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="M732" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="N732" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="O732" s="2"/>
       <c r="P732" s="2"/>
@@ -82302,13 +82305,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82405,13 +82408,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82508,13 +82511,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82554,7 +82557,7 @@
       </c>
       <c r="R735" s="2"/>
       <c r="S735" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="T735" t="s" s="2">
         <v>75</v>
@@ -82613,13 +82616,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82642,7 +82645,7 @@
         <v>75</v>
       </c>
       <c r="L736" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="M736" t="s" s="2">
         <v>1007</v>
@@ -82687,7 +82690,7 @@
         <v>75</v>
       </c>
       <c r="AC736" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="AD736" s="2"/>
       <c r="AE736" t="s" s="2">
@@ -82714,16 +82717,16 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D737" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E737" t="s" s="2">
         <v>75</v>
@@ -82745,7 +82748,7 @@
         <v>75</v>
       </c>
       <c r="L737" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="M737" t="s" s="2">
         <v>1007</v>
@@ -82819,13 +82822,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82924,13 +82927,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83029,13 +83032,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83134,13 +83137,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83239,7 +83242,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1178</v>
@@ -83346,7 +83349,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1185</v>
@@ -83378,7 +83381,7 @@
         <v>1186</v>
       </c>
       <c r="M743" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="N743" t="s" s="2">
         <v>1188</v>
@@ -83449,7 +83452,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1189</v>
@@ -83481,7 +83484,7 @@
         <v>259</v>
       </c>
       <c r="M744" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="N744" t="s" s="2">
         <v>1191</v>
@@ -83554,7 +83557,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1194</v>
@@ -83657,7 +83660,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1195</v>
@@ -83762,7 +83765,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1196</v>
@@ -83869,7 +83872,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1197</v>
@@ -83976,7 +83979,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1204</v>
@@ -84085,7 +84088,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1211</v>
@@ -84190,7 +84193,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1215</v>
@@ -84219,10 +84222,10 @@
         <v>75</v>
       </c>
       <c r="L751" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="M751" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="N751" t="s" s="2">
         <v>1218</v>
@@ -84293,7 +84296,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1219</v>

--- a/cp-card-custodian/ig/all-profiles.xlsx
+++ b/cp-card-custodian/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24995" uniqueCount="1336">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:29:51+00:00</t>
+    <t>2026-05-28T14:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -825,10 +825,10 @@
 </t>
   </si>
   <si>
-    <t>Organisme responsable de la gestion du document. Information transmise dans le VIHF.</t>
-  </si>
-  <si>
-    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+    <t>Organisme responsable de la gestion du document. Dans le cadre XDS, il s'agit d'une information transmise dans le VIHF.</t>
+  </si>
+  <si>
+    <t>Correspond à l’organisation responsable de la conservation, de la maintenance et/ou de l’accès au document, et non nécessairement à l’auteur ou à l’hébergeur technique.</t>
   </si>
   <si>
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
@@ -3898,9 +3898,6 @@
   </si>
   <si>
     <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif.</t>
-  </si>
-  <si>
-    <t>Organisme responsable de la gestion du document. Dans le cadre XDS, il s'agit d'une information transmise dans le VIHF.</t>
   </si>
   <si>
     <t>Relationships to other documents</t>
@@ -5669,7 +5666,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="174">
@@ -5677,7 +5674,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="175">
@@ -5693,7 +5690,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="177">
@@ -5701,7 +5698,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="178">
@@ -5755,7 +5752,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="185">
@@ -5799,7 +5796,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="191">
@@ -73868,7 +73865,7 @@
         <v>254</v>
       </c>
       <c r="M652" t="s" s="2">
-        <v>1245</v>
+        <v>255</v>
       </c>
       <c r="N652" t="s" s="2">
         <v>256</v>
@@ -73973,10 +73970,10 @@
         <v>259</v>
       </c>
       <c r="M653" t="s" s="2">
+        <v>1245</v>
+      </c>
+      <c r="N653" t="s" s="2">
         <v>1246</v>
-      </c>
-      <c r="N653" t="s" s="2">
-        <v>1247</v>
       </c>
       <c r="O653" t="s" s="2">
         <v>262</v>
@@ -74393,7 +74390,7 @@
         <v>159</v>
       </c>
       <c r="M657" t="s" s="2">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="N657" t="s" s="2">
         <v>274</v>
@@ -74498,7 +74495,7 @@
         <v>279</v>
       </c>
       <c r="M658" t="s" s="2">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="N658" t="s" s="2">
         <v>281</v>
@@ -74815,7 +74812,7 @@
         <v>259</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>296</v>
@@ -75754,7 +75751,7 @@
         <v>321</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>323</v>
@@ -75861,7 +75858,7 @@
         <v>328</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>330</v>
@@ -76287,7 +76284,7 @@
         <v>356</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>358</v>
@@ -77290,7 +77287,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="685">
@@ -77395,7 +77392,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="686">
@@ -77608,7 +77605,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1099</v>
@@ -77711,7 +77708,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1101</v>
@@ -77816,7 +77813,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1102</v>
@@ -77919,7 +77916,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1103</v>
@@ -78022,7 +78019,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1104</v>
@@ -78127,7 +78124,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1105</v>
@@ -78232,7 +78229,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1106</v>
@@ -78337,7 +78334,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1107</v>
@@ -78442,7 +78439,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1108</v>
@@ -78547,7 +78544,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1109</v>
@@ -78652,7 +78649,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1110</v>
@@ -78757,7 +78754,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1111</v>
@@ -78862,7 +78859,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1112</v>
@@ -78967,7 +78964,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1113</v>
@@ -79072,7 +79069,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1114</v>
@@ -79104,7 +79101,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79177,7 +79174,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1116</v>
@@ -79191,7 +79188,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79278,7 +79275,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1117</v>
@@ -79312,7 +79309,7 @@
         <v>1119</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1121</v>
@@ -79378,18 +79375,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1264</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1265</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1266</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79486,13 +79483,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1266</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1267</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1268</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79589,13 +79586,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1268</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1269</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1270</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79635,7 +79632,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79694,13 +79691,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1271</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1272</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1273</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79760,13 +79757,13 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
+        <v>1273</v>
+      </c>
+      <c r="AB708" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC708" t="s" s="2">
         <v>1274</v>
-      </c>
-      <c r="AB708" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC708" t="s" s="2">
-        <v>1275</v>
       </c>
       <c r="AD708" s="2"/>
       <c r="AE708" t="s" s="2">
@@ -79793,16 +79790,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1275</v>
+      </c>
+      <c r="C709" t="s" s="2">
+        <v>1272</v>
+      </c>
+      <c r="D709" t="s" s="2">
         <v>1276</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1273</v>
-      </c>
-      <c r="D709" t="s" s="2">
-        <v>1277</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79898,16 +79895,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79929,13 +79926,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
+        <v>1279</v>
+      </c>
+      <c r="M710" t="s" s="2">
         <v>1280</v>
       </c>
-      <c r="M710" t="s" s="2">
+      <c r="N710" t="s" s="2">
         <v>1281</v>
-      </c>
-      <c r="N710" t="s" s="2">
-        <v>1282</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -80003,16 +80000,16 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D711" t="s" s="2">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E711" t="s" s="2">
         <v>75</v>
@@ -80034,13 +80031,13 @@
         <v>75</v>
       </c>
       <c r="L711" t="s" s="2">
+        <v>1284</v>
+      </c>
+      <c r="M711" t="s" s="2">
         <v>1285</v>
       </c>
-      <c r="M711" t="s" s="2">
+      <c r="N711" t="s" s="2">
         <v>1286</v>
-      </c>
-      <c r="N711" t="s" s="2">
-        <v>1287</v>
       </c>
       <c r="O711" s="2"/>
       <c r="P711" s="2"/>
@@ -80108,10 +80105,10 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1116</v>
@@ -80142,7 +80139,7 @@
         <v>187</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>189</v>
@@ -80213,16 +80210,16 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C713" t="s" s="2">
         <v>1116</v>
       </c>
       <c r="D713" t="s" s="2">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E713" t="s" s="2">
         <v>75</v>
@@ -80244,10 +80241,10 @@
         <v>75</v>
       </c>
       <c r="L713" t="s" s="2">
+        <v>1291</v>
+      </c>
+      <c r="M713" t="s" s="2">
         <v>1292</v>
-      </c>
-      <c r="M713" t="s" s="2">
-        <v>1293</v>
       </c>
       <c r="N713" t="s" s="2">
         <v>994</v>
@@ -80318,13 +80315,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80421,13 +80418,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80524,13 +80521,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80629,13 +80626,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -80658,7 +80655,7 @@
         <v>75</v>
       </c>
       <c r="L717" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="M717" t="s" s="2">
         <v>1007</v>
@@ -80732,7 +80729,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1122</v>
@@ -80835,7 +80832,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1123</v>
@@ -80936,7 +80933,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1126</v>
@@ -80967,10 +80964,10 @@
         <v>75</v>
       </c>
       <c r="L720" t="s" s="2">
+        <v>1298</v>
+      </c>
+      <c r="M720" t="s" s="2">
         <v>1299</v>
-      </c>
-      <c r="M720" t="s" s="2">
-        <v>1300</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>196</v>
@@ -81041,7 +81038,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1129</v>
@@ -81075,7 +81072,7 @@
         <v>206</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>196</v>
@@ -81146,7 +81143,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1131</v>
@@ -81178,7 +81175,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1133</v>
@@ -81251,7 +81248,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1137</v>
@@ -81283,7 +81280,7 @@
         <v>159</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1139</v>
@@ -81358,7 +81355,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1145</v>
@@ -81390,7 +81387,7 @@
         <v>98</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1147</v>
@@ -81463,7 +81460,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1150</v>
@@ -81495,7 +81492,7 @@
         <v>221</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1152</v>
@@ -81514,7 +81511,7 @@
         <v>75</v>
       </c>
       <c r="T725" t="s" s="2">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="U725" t="s" s="2">
         <v>75</v>
@@ -81568,7 +81565,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1157</v>
@@ -81675,7 +81672,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81778,7 +81775,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1166</v>
@@ -81810,7 +81807,7 @@
         <v>356</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1168</v>
@@ -81885,7 +81882,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1171</v>
@@ -81917,7 +81914,7 @@
         <v>244</v>
       </c>
       <c r="M729" t="s" s="2">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="N729" t="s" s="2">
         <v>1175</v>
@@ -81992,13 +81989,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82095,13 +82092,13 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B731" t="s" s="2">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C731" t="s" s="2">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="D731" s="2"/>
       <c r="E731" t="s" s="2">
@@ -82200,16 +82197,16 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1310</v>
+      </c>
+      <c r="C732" t="s" s="2">
+        <v>1309</v>
+      </c>
+      <c r="D732" t="s" s="2">
         <v>1311</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1310</v>
-      </c>
-      <c r="D732" t="s" s="2">
-        <v>1312</v>
       </c>
       <c r="E732" t="s" s="2">
         <v>75</v>
@@ -82231,13 +82228,13 @@
         <v>75</v>
       </c>
       <c r="L732" t="s" s="2">
+        <v>1312</v>
+      </c>
+      <c r="M732" t="s" s="2">
         <v>1313</v>
       </c>
-      <c r="M732" t="s" s="2">
+      <c r="N732" t="s" s="2">
         <v>1314</v>
-      </c>
-      <c r="N732" t="s" s="2">
-        <v>1315</v>
       </c>
       <c r="O732" s="2"/>
       <c r="P732" s="2"/>
@@ -82305,13 +82302,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1316</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1317</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82408,13 +82405,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1318</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1319</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82511,13 +82508,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1319</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1320</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1321</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82557,7 +82554,7 @@
       </c>
       <c r="R735" s="2"/>
       <c r="S735" t="s" s="2">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="T735" t="s" s="2">
         <v>75</v>
@@ -82616,13 +82613,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1322</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1323</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1324</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82645,7 +82642,7 @@
         <v>75</v>
       </c>
       <c r="L736" t="s" s="2">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="M736" t="s" s="2">
         <v>1007</v>
@@ -82690,7 +82687,7 @@
         <v>75</v>
       </c>
       <c r="AC736" t="s" s="2">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="AD736" s="2"/>
       <c r="AE736" t="s" s="2">
@@ -82717,16 +82714,16 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1325</v>
+      </c>
+      <c r="C737" t="s" s="2">
+        <v>1323</v>
+      </c>
+      <c r="D737" t="s" s="2">
         <v>1326</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1324</v>
-      </c>
-      <c r="D737" t="s" s="2">
-        <v>1327</v>
       </c>
       <c r="E737" t="s" s="2">
         <v>75</v>
@@ -82748,7 +82745,7 @@
         <v>75</v>
       </c>
       <c r="L737" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="M737" t="s" s="2">
         <v>1007</v>
@@ -82822,13 +82819,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82927,13 +82924,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -83032,13 +83029,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83137,13 +83134,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83242,7 +83239,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1178</v>
@@ -83349,7 +83346,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1185</v>
@@ -83381,7 +83378,7 @@
         <v>1186</v>
       </c>
       <c r="M743" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="N743" t="s" s="2">
         <v>1188</v>
@@ -83452,7 +83449,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1189</v>
@@ -83484,7 +83481,7 @@
         <v>259</v>
       </c>
       <c r="M744" t="s" s="2">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="N744" t="s" s="2">
         <v>1191</v>
@@ -83557,7 +83554,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1194</v>
@@ -83660,7 +83657,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1195</v>
@@ -83765,7 +83762,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1196</v>
@@ -83872,7 +83869,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1197</v>
@@ -83979,7 +83976,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1204</v>
@@ -84088,7 +84085,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1211</v>
@@ -84193,7 +84190,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1215</v>
@@ -84222,10 +84219,10 @@
         <v>75</v>
       </c>
       <c r="L751" t="s" s="2">
+        <v>1334</v>
+      </c>
+      <c r="M751" t="s" s="2">
         <v>1335</v>
-      </c>
-      <c r="M751" t="s" s="2">
-        <v>1336</v>
       </c>
       <c r="N751" t="s" s="2">
         <v>1218</v>
@@ -84296,7 +84293,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1219</v>
